--- a/NOP_BAI_23120231_HW01/03_Excel/R3_TestCases_Checklist_Summary.xlsx
+++ b/NOP_BAI_23120231_HW01/03_Excel/R3_TestCases_Checklist_Summary.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lần bấm, phím trước nảy lên và phím mới chìm xuống. Động cơ chạy ở cả 3 cấp, gió tăng dần. Bấm 0 thì phím 3 nảy lên, cánh giảm tốc theo quán tính rồi dừng hẳn, không rè, không rung bất thường.</t>
+          <t xml:space="preserve">Tôi bấm 1 2 3 rồi 0, quạt hoạt động bình thường.</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Khi ấn chốt, đầu quạt quét đều hai bên, không kêu lục cục, không khựng. Khi kéo chốt lên, quạt dừng quét ngay tại vị trí đang đứng và giữ nguyên hướng thổi, cánh vẫn quay bình thường.</t>
+          <t xml:space="preserve">Ban đầu đang quay, ấn chốt nó đứng và ấn lại nó quay lại.</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Sau khi buông tay, khớp gập giữ nguyên góc ở cả hai vị trí (ngửa hết cỡ và cúi hết cỡ) trong suốt 30 giây quan sát. Không tự trôi, không gục xuống dưới phản lực gió ở số 3.</t>
+          <t>Khớp giữ nguyên góc trong 30 giây, không bị trôi.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Toàn bộ thông tin bắt buộc trên tem còn đọc rõ: hãng SENKO, 220V/50Hz/40W, cấp cách điện E, cấp chống giật điện cấp 0, TCVN 5699-2-80:2007 (IEC 60335-2-80:2005), lô SX 107, tháng SX 07-2022. Chà nhẹ mặt tem 5 lần, chữ không nhòe. Tem bám chắc, không bong góc, không bị che khuất.</t>
+          <t>Tem chữ còn rõ sau khi chà.</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Đánh giá bằng tai, không dùng thiết bị đo. Độ ồn tăng dần qua ba cấp, cấp 3 ồn nhất. Chỉ nghe thấy tiếng gió và tiếng động cơ đều; không có tiếng lạch cạch theo nhịp, không tiếng rít kim loại, không tiếng va đập từ hộp tuốc năng.</t>
+          <t>Chạy êm, chỉ nghe tiếng gió.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Không quan sát thấy tia lửa tại chân phích khi cắm lại. Động cơ khởi động lại ngay, cánh đạt lại tốc độ bình thường, không kẹt rotor, không có tiếng ù kéo dài.</t>
+          <t>Động cơ chạy lại bình thường.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Độ bay của tờ giấy tăng rõ rệt qua từng cấp: cấp 1 giấy lay nhẹ, cấp 2 bay mạnh hơn, cấp 3 bay mạnh nhất. Ba cấp phân biệt được bằng mắt thường, không có hai cấp nào cho kết quả giống nhau.</t>
+          <t xml:space="preserve">Giấy bay mạnh theo từ cấp 1 - 3.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Quạt không nhận cấp tốc độ nào. Cả hai phím đều nảy lên vị trí ngắt, động cơ mất điện và dừng hẳn. Phải bấm lại một lần nữa quạt mới chạy. Tái hiện 3/3 lần. Ngưỡng quan sát: bấm cách nhau từ 0,5 giây trở lên thì chuyển cấp bình thường, nhanh hơn thì quạt tắt.</t>
+          <t>Quạt tắt ngúm, cả hai phím nảy lên.</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Cánh tự quay sau khoảng 1 giây, không có tiếng ù.</t>
+          <t>Bật số 1 cánh quay ngay sau khoảng 1 giây.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Quét được ở cả ba cấp, biên độ ba lần đo như nhau.</t>
+          <t xml:space="preserve">Quạt xoay đều 3 chế độ, biên độ như nhau.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Không chạm được cánh ở mọi vị trí thử.</t>
+          <t>Tay không chạm tới cánh.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1197,27 +1197,27 @@
     <row r="13" ht="120" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC14</t>
+          <t>TC14</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sinh viên</t>
+          <t>Sinh viên</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kiểm tra yêu cầu an toàn: lồng bảo vệ chỉ được tháo ra khi dùng dụng cụ, theo TCVN 5699-2-80.</t>
+          <t>Kiểm tra yêu cầu an toàn: lồng bảo vệ chỉ được tháo ra khi dùng dụng cụ, theo TCVN 5699-2-80.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quạt đã RÚT ĐIỆN; chỉ dùng tay không, không dùng tua vít hay kìm.</t>
+          <t>Quạt đã RÚT ĐIỆN; chỉ dùng tay không, không dùng tua vít hay kìm.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Rút phích điện, chờ cánh dừng hẳn.
+          <t>1. Rút phích điện, chờ cánh dừng hẳn.
 2. Thử bật các kẹp/khóa lồng bằng tay không.
 3. Thử xoay vòng khóa lồng bằng tay không.
 4. Ghi nhận có tháo được lồng trước ra không.</t>
@@ -1225,28 +1225,28 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Không tháo được lồng bảo vệ nếu không dùng dụng cụ.</t>
+          <t>Không tháo được lồng bảo vệ nếu không dùng dụng cụ.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lồng bảo vệ tháo được bằng tay không khá dễ dàng, các chốt nhựa có thể bật ra bằng ngón tay.</t>
+          <t xml:space="preserve">Tháo dễ dàng bằng tay không.</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inconclusive</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
+          <t>Inconclusive</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quan sát trực tiếp (không quay video)</t>
+          <t>Quan sát trực tiếp (không quay video)</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">đã chạy</t>
+          <t>đã chạy</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Cánh vẫn quay bình thường nhưng hành trình quét bị dịch hẳn sang một bên; hai điểm cuối không còn trùng mốc ban đầu. Quạt không tự phục hồi dù chạy tiếp, phải tắt và chỉnh lại bằng tay. Tái hiện 2/2 lần.</t>
+          <t>Góc quét bị lệch hẳn sang một bên, phải vặn tay lại.</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Vỏ cách điện liền lạc trên toàn bộ chiều dài dây, không nứt, không chai cứng, không cháy xém. Chân phích thẳng và chắc, không gỉ. Kéo nhẹ dây tại điểm vào thân quạt, dây không xê dịch, không lộ lõi đồng.</t>
+          <t>Dây điện bình thường.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Sau 3 phút chạy số 3 kèm đảo gió, đồng xu vẫn nằm nguyên trên đế, không trượt, không rơi. Chân đế không lệch khỏi vạch băng keo đánh dấu. Không quan sát thấy rung lắc thân quạt bằng mắt thường.</t>
+          <t>Quạt đứng vững không rung lắc.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Xem R3_edge_cases_explanation.md — mỗi case kèm đối chiếu với danh sách 8 test case của Gemini</t>
+          <t>Xem báo cáo chính, mục "R3 — Ba edge case AI không tìm ra" — mỗi case kèm đối chiếu với danh sách 8 test case của Gemini</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>R3_edge_cases_explanation.md — sinh viên viết, đối chiếu trực tiếp với từng test case Gemini đã sinh</t>
+          <t>Báo cáo chính, mục "R3 — Ba edge case AI không tìm ra" — Claude soạn nháp, sinh viên soát lại và sửa lập luận TC13 (khai tại [AI-02] Artifact #15); đối chiếu trực tiếp với từng test case Gemini đã sinh</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 video: TC01, TC02, TC09, TC10, TC15. Cả 2 defect đều nằm trong số này.</t>
+          <t>5 video: TC01, TC02, TC09, TC10, TC15. Cả 2 defect đều nằm trong số này.</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 defect</t>
+          <t>2 defect</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 defect có thật, cả hai đều có video. TC14 ghi Inconclusive vì không có test oracle kiểm chứng được. Đề ghi "aim to find ≥5" là mục tiêu chứ không phải yêu cầu cứng; phần KẾT LUẬN đã giải thích vì sao không hạ tiêu chí Pass để tăng số lượng.</t>
+          <t>2 defect có thật, cả hai đều có video. TC14 ghi Inconclusive vì không có test oracle kiểm chứng được. Đề ghi "aim to find ≥5" là mục tiêu chứ không phải yêu cầu cứng; phần KẾT LUẬN đã giải thích vì sao không hạ tiêu chí Pass để tăng số lượng.</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 issue: DEF-01 (#1), DEF-02 (#3) tại github.com/nhaajtdajt/HW01/issues</t>
+          <t>2 issue: DEF-01 (#1), DEF-02 (#3) tại github.com/nhaajtdajt/HW01/issues</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">evidence/github_issues.png — thấy rõ username nhaajtdajt và 2 issue đang Open</t>
+          <t>evidence/github_issues.png — thấy rõ username nhaajtdajt và 2 issue đang Open</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Đầy đủ: thiết bị, môi trường, kết quả, defect, nguồn gốc test case, lý do hoãn, kết luận</t>
+          <t>Đầy đủ: thiết bị, môi trường, kết quả, defect, nguồn gốc test case, lý do loại test case, kết luận</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 — TC01, TC02, TC03, TC05, TC06, TC07, TC09, TC11, TC12, TC13, TC16, TC17</t>
+          <t>12 — TC01, TC02, TC03, TC05, TC06, TC07, TC09, TC11, TC12, TC13, TC16, TC17</t>
         </is>
       </c>
     </row>
@@ -2117,19 +2117,19 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 — TC10, TC15</t>
+          <t>2 — TC10, TC15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inconclusive / Chưa chạy</t>
+          <t>Inconclusive / Chưa chạy</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Inconclusive — TC14 (không có test oracle kiểm chứng được, xem KẾT LUẬN) / 0 chưa chạy</t>
+          <t>1 Inconclusive — TC14 (không có test oracle kiểm chứng được, xem KẾT LUẬN) / 0 chưa chạy</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/15 = 80%</t>
+          <t>12/15 = 80%</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 defect xác nhận, cả hai đều có video: DEF-01 (TC10), DEF-02 (TC15)</t>
+          <t>2 defect xác nhận, cả hai đều có video: DEF-01 (TC10), DEF-02 (TC15)</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical 0 / High 0 / Medium 2 (DEF-01, DEF-02) / Low 0</t>
+          <t>Critical 0 / High 0 / Medium 2 (DEF-01, DEF-02) / Low 0</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://github.com/nhaajtdajt/HW01/issues — 2 issue: DEF-01 (#1), DEF-02 (#3)</t>
+          <t>https://github.com/nhaajtdajt/HW01/issues — 2 issue: DEF-01 (#1), DEF-02 (#3)</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toàn bộ 15 test case đã được thực thi trên thiết bị thật: 12 Pass, 2 Fail, 1 Inconclusive.
+          <t>Toàn bộ 15 test case đã được thực thi trên thiết bị thật: 12 Pass, 2 Fail, 1 Inconclusive.
 Thiết bị vận hành đúng các chức năng cơ bản. Ba cấp gió phân biệt rõ bằng quan sát, cơ cấu đảo gió đóng ngắt đúng và giữ nguyên biên độ ở cả ba cấp, động cơ tự khởi động được ở cấp thấp nhất khi nguội, khớp gập cổ giữ góc ổn định ở tốc độ cao nhất, dây nguồn và phích cắm còn nguyên vẹn, nhãn thông số còn đọc rõ, và khe nan lồng không cho ngón tay chạm tới cánh.
 Hai defect được phát hiện, cả hai đều có video. DEF-01: quạt tắt hẳn thay vì chuyển cấp khi bấm hai phím tốc độ cách nhau dưới 0,5 giây, tái hiện 3/3 lần. DEF-02: hành trình quét của tuốc năng lệch vĩnh viễn sau khi đầu quạt bị đẩy quá điểm cuối, không tự phục hồi mà phải tắt và chỉnh tay, tái hiện 2/2 lần. Cả hai không gây mất an toàn nhưng đều xảy ra trong thao tác thường ngày.
 TC14 ghi Inconclusive: quan sát thực tế là lồng bảo vệ trước tháo được bằng tay không khi đã rút điện. Expected Result của TC14 ("chỉ tháo được khi dùng dụng cụ") dựa trên TCVN 5699-2-80 mà tem thiết bị công bố, nhưng chưa tra được nguyên văn điều khoản (tiêu chuẩn không công bố miễn phí), nên không có test oracle kiểm chứng được để kết luận Pass hay Fail. Quan sát được ghi lại đầy đủ nhưng không nâng thành defect. Yêu cầu chống chạm cánh đã được kiểm riêng ở TC13 và đạt.
